--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_302_R31.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_302_R31.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.483700000000001</v>
+        <v>8.332800000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0679</v>
+        <v>8.1858</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4159</v>
+        <v>0.147</v>
       </c>
       <c r="G2" t="n">
         <v>4.0011</v>
@@ -610,13 +610,13 @@
         <v>0.232</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2634</v>
+        <v>1.1125</v>
       </c>
       <c r="T2" t="n">
-        <v>0.13</v>
+        <v>0.248</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1334</v>
+        <v>0.8646</v>
       </c>
       <c r="V2" t="n">
         <v>4.147</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2922</v>
+        <v>3.1376</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5427</v>
+        <v>2.1715</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7495</v>
+        <v>0.9661</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8941</v>
+        <v>0.8881</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1814</v>
+        <v>1.9687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7127</v>
+        <v>-1.0807</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7297</v>
+        <v>2.0494</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0672</v>
+        <v>1.8654</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6625</v>
+        <v>0.184</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1644</v>
+        <v>-1.1613</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1141</v>
+        <v>0.1034</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0502</v>
+        <v>-1.2647</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1598</v>
+        <v>2.7834</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3079</v>
+        <v>-0.3921</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9006</v>
+        <v>0.1221</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5926</v>
+        <v>-0.5142</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9304</v>
+        <v>-0.1418</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>-0.1418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.88</v>
+        <v>2.7435</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9475</v>
+        <v>1.0276</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9325</v>
+        <v>1.7159</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8881</v>
+        <v>0.8941</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9687</v>
+        <v>0.1814</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0807</v>
+        <v>0.7127</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0494</v>
+        <v>0.7297</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8654</v>
+        <v>0.0672</v>
       </c>
       <c r="L4" t="n">
-        <v>0.184</v>
+        <v>0.6625</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1613</v>
+        <v>0.1644</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1034</v>
+        <v>0.1141</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2647</v>
+        <v>0.0502</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7834</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7834</v>
+        <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6497000000000001</v>
+        <v>-0.2407</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1019</v>
+        <v>0.3855</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5478</v>
+        <v>-0.6262</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1418</v>
+        <v>0.9304</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
         <v>-0.1418</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8679</v>
+        <v>1.8265</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9663</v>
+        <v>1.6982</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9016</v>
+        <v>0.1284</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6027</v>
+        <v>2.5623</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.09</v>
+        <v>2.2075</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6928</v>
+        <v>0.3549</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8204</v>
+        <v>3.202</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1211</v>
+        <v>2.9444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6993</v>
+        <v>0.2576</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2177</v>
+        <v>-0.6397</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2112</v>
+        <v>-0.7369</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0065</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8888</v>
+        <v>1.1224</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7695</v>
+        <v>0.4446</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1193</v>
+        <v>0.6778</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5361</v>
+        <v>-0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5361</v>
+        <v>-0.7886</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2311</v>
+        <v>1.6558</v>
       </c>
       <c r="E6" t="n">
-        <v>2.17</v>
+        <v>1.1774</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0611</v>
+        <v>0.4784</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5623</v>
+        <v>-0.4539</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2075</v>
+        <v>-0.3602</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3549</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>3.202</v>
+        <v>0.3929</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9444</v>
+        <v>-0.4636</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2576</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6397</v>
+        <v>-0.8468</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7369</v>
+        <v>0.1034</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09719999999999999</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>1.527</v>
+        <v>-0.4933</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9164</v>
+        <v>-0.0351</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6106</v>
+        <v>-0.4582</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9304</v>
+        <v>0.2836</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7886</v>
+        <v>0.8197</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4393</v>
+        <v>1.6047</v>
       </c>
       <c r="E7" t="n">
-        <v>1.028</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4112</v>
+        <v>0.7</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4539</v>
+        <v>0.6027</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3602</v>
+        <v>-0.09</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09370000000000001</v>
+        <v>0.6928</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3929</v>
+        <v>0.8204</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4636</v>
+        <v>0.1211</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.6993</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8468</v>
+        <v>-0.2177</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1034</v>
+        <v>-0.2112</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.0065</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3195</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7099</v>
+        <v>1.6256</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1845</v>
+        <v>0.7079</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5254</v>
+        <v>0.9177</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2836</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8197</v>
+        <v>0.5361</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2156</v>
+        <v>1.2641</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0069</v>
+        <v>0.1562</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2087</v>
+        <v>1.1079</v>
       </c>
       <c r="G8" t="n">
         <v>0.3626</v>
@@ -1078,13 +1078,13 @@
         <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4485</v>
+        <v>-0.4</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1845</v>
+        <v>-0.0351</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.264</v>
+        <v>-0.3648</v>
       </c>
       <c r="V8" t="n">
         <v>0.1418</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.54</v>
+        <v>0.6893</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6051</v>
+        <v>2.7545</v>
       </c>
       <c r="F9" t="n">
         <v>-2.0651</v>
@@ -1156,10 +1156,10 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.224</v>
+        <v>-0.0747</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2829</v>
+        <v>-0.1336</v>
       </c>
       <c r="U9" t="n">
         <v>0.0589</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9257</v>
+        <v>-0.3514</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.6622</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1299</v>
+        <v>0.3108</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2631</v>
+        <v>-1.2193</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4405</v>
+        <v>-0.4261</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1774</v>
+        <v>-0.7931</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6623</v>
+        <v>-0.8551</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7359</v>
+        <v>-0.383</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0736</v>
+        <v>-0.4721</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6008</v>
+        <v>-0.3642</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7045</v>
+        <v>-0.0431</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1038</v>
+        <v>-0.3211</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3585</v>
+        <v>0.8678</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1336</v>
+        <v>0.1928</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2249</v>
+        <v>0.675</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.16</v>
+        <v>-0.7166</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3699</v>
+        <v>-0.7212</v>
       </c>
       <c r="F11" t="n">
-        <v>0.21</v>
+        <v>0.0046</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2193</v>
+        <v>-1.2631</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4261</v>
+        <v>-1.4405</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7931</v>
+        <v>0.1774</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8551</v>
+        <v>-0.6623</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.383</v>
+        <v>-0.7359</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4721</v>
+        <v>0.0736</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3642</v>
+        <v>-0.6008</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0431</v>
+        <v>-0.7045</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3211</v>
+        <v>0.1038</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0593</v>
+        <v>-0.1494</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5149</v>
+        <v>-0.0589</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5742</v>
+        <v>-0.0905</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9499</v>
+        <v>-4.9995</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2567</v>
+        <v>-3.4743</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6932</v>
+        <v>-1.5252</v>
       </c>
       <c r="G12" t="n">
         <v>-5.7733</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1946</v>
+        <v>0.7558</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4991</v>
+        <v>0.2833</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3044</v>
+        <v>0.4725</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6778999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.5701</v>
+        <v>-5.7227</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.8124</v>
+        <v>-6.9986</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2423</v>
+        <v>1.2759</v>
       </c>
       <c r="G13" t="n">
         <v>-3.2784</v>
@@ -1468,13 +1468,13 @@
         <v>2.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4361</v>
+        <v>-0.5887</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8883</v>
+        <v>-0.0745</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5478</v>
+        <v>-0.5142</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,34 +1501,34 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.344100000000005</v>
+        <v>9.464099999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>5.099500000000001</v>
+        <v>6.219600000000003</v>
       </c>
       <c r="F14" t="n">
-        <v>3.244599999999999</v>
+        <v>3.244699999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-1.678500000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.948199999999999</v>
+        <v>0.9482000000000008</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.626500000000001</v>
+        <v>-2.6265</v>
       </c>
       <c r="J14" t="n">
         <v>7.3262</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1157</v>
+        <v>4.115699999999999</v>
       </c>
       <c r="L14" t="n">
         <v>3.2105</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.004999999999999</v>
+        <v>-9.005000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-3.1675</v>
@@ -1546,13 +1546,13 @@
         <v>15.077</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0251</v>
+        <v>3.1452</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9268000000000002</v>
+        <v>2.047</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0983</v>
+        <v>1.0984</v>
       </c>
       <c r="V14" t="n">
         <v>3.3584</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3891</v>
+        <v>2.6377</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9294</v>
+        <v>2.4576</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4597</v>
+        <v>0.1801</v>
       </c>
       <c r="G15" t="n">
         <v>1.9673</v>
@@ -1624,13 +1624,13 @@
         <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3675</v>
+        <v>0.6161</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2715</v>
+        <v>-0.2003</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0961</v>
+        <v>0.8164</v>
       </c>
       <c r="V15" t="n">
         <v>1.214</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.133</v>
+        <v>2.5313</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3899</v>
+        <v>1.2719</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7432</v>
+        <v>1.2594</v>
       </c>
       <c r="G16" t="n">
         <v>1.6173</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.644</v>
+        <v>-0.2458</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1845</v>
+        <v>-0.3025</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4595</v>
+        <v>0.0567</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5077</v>
+        <v>0.7889</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6113</v>
+        <v>2.9981</v>
       </c>
       <c r="F17" t="n">
-        <v>1.119</v>
+        <v>-2.2092</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4506</v>
+        <v>2.6407</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0324</v>
+        <v>1.443</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4182</v>
+        <v>1.1977</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4034</v>
+        <v>4.6995</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4636</v>
+        <v>2.7056</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0602</v>
+        <v>1.9939</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0472</v>
+        <v>-2.0587</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5688</v>
+        <v>-1.2626</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4783</v>
+        <v>-0.7961</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6568000000000001</v>
+        <v>-0.4059</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1142</v>
+        <v>-0.8252</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5425</v>
+        <v>0.4193</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1418</v>
+        <v>-1.214</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>0.2836</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4975</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4417</v>
+        <v>0.734</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5496</v>
+        <v>-0.3221</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1079</v>
+        <v>1.0561</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2276</v>
+        <v>-0.2774</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1129</v>
+        <v>-1.0302</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1147</v>
+        <v>0.7528</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7312</v>
+        <v>0.8449</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8739</v>
+        <v>-0.4398</v>
       </c>
       <c r="L18" t="n">
-        <v>2.8573</v>
+        <v>1.2847</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5036</v>
+        <v>-1.1222</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2391</v>
+        <v>-0.5904</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7426</v>
+        <v>-0.5319</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.9278</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-2.7834</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-3.9432</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0697</v>
+        <v>0.4727</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7616</v>
+        <v>0.0081</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6919</v>
+        <v>0.4646</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>1.4665</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3355</v>
+        <v>0.5477</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7295</v>
+        <v>-0.4933</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.394</v>
+        <v>1.041</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0647</v>
+        <v>-1.4506</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0781</v>
+        <v>-1.0324</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0133</v>
+        <v>-0.4182</v>
       </c>
       <c r="J19" t="n">
-        <v>1.458</v>
+        <v>-0.4034</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3108</v>
+        <v>-0.4636</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1472</v>
+        <v>0.0602</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3933</v>
+        <v>-1.0472</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2327</v>
+        <v>-0.5688</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1605</v>
+        <v>-0.4783</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5153</v>
+        <v>0.6967</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2715</v>
+        <v>0.2322</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.4646</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2885</v>
+        <v>0.4921</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6442</v>
+        <v>1.4936</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3557</v>
+        <v>-1.0015</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6407</v>
+        <v>1.0647</v>
       </c>
       <c r="H20" t="n">
-        <v>1.443</v>
+        <v>1.0781</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1977</v>
+        <v>-0.0133</v>
       </c>
       <c r="J20" t="n">
-        <v>4.6995</v>
+        <v>1.458</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7056</v>
+        <v>1.3108</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9939</v>
+        <v>0.1472</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0587</v>
+        <v>-0.3933</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2626</v>
+        <v>-0.2327</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7961</v>
+        <v>-0.1605</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9063</v>
+        <v>-0.3587</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1791</v>
+        <v>0.0356</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2728</v>
+        <v>-0.3943</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.214</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4975</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3383</v>
+        <v>-0.1652</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9119</v>
+        <v>0.3701</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5736</v>
+        <v>-0.5353</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2774</v>
+        <v>3.2276</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0302</v>
+        <v>1.1129</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7528</v>
+        <v>2.1147</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8449</v>
+        <v>3.7312</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4398</v>
+        <v>0.8739</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2847</v>
+        <v>2.8573</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1222</v>
+        <v>-0.5036</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5904</v>
+        <v>0.2391</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5319</v>
+        <v>-0.7426</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9278</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7834</v>
+        <v>-3.9432</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5996</v>
+        <v>0.4628</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5816</v>
+        <v>0.5821</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.018</v>
+        <v>-0.1193</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4665</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.251</v>
+        <v>-1.2117</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1858</v>
+        <v>-1.3038</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.06510000000000001</v>
+        <v>0.0921</v>
       </c>
       <c r="G22" t="n">
         <v>0.1458</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1573</v>
+        <v>0.1966</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3383</v>
+        <v>0.2203</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.181</v>
+        <v>-0.0237</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3943</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.924</v>
+        <v>-1.2277</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3027</v>
+        <v>-0.8309</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6213</v>
+        <v>-0.3968</v>
       </c>
       <c r="G23" t="n">
         <v>0.0261</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5764</v>
+        <v>0.1199</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2829</v>
+        <v>0.1889</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2934</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6778999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6627</v>
+        <v>-4.326</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5578</v>
+        <v>-2.3219</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.105</v>
+        <v>-2.0041</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2201</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7622</v>
+        <v>-0.4255</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.731</v>
+        <v>-0.4951</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0312</v>
+        <v>0.0696</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1444</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.2636</v>
+        <v>-6.7861</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.776</v>
+        <v>-6.4222</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4875</v>
+        <v>-0.3639</v>
       </c>
       <c r="G25" t="n">
         <v>-5.0631</v>
@@ -2404,13 +2404,13 @@
         <v>0.232</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2727</v>
+        <v>-0.7951</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8962</v>
+        <v>-0.5423</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3765</v>
+        <v>-0.2528</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.344100000000001</v>
+        <v>-5.984999999999999</v>
       </c>
       <c r="E26" t="n">
         <v>-3.1029</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.241000000000001</v>
+        <v>-2.8821</v>
       </c>
       <c r="G26" t="n">
         <v>1.678299999999998</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9479999999999997</v>
+        <v>-0.9480000000000002</v>
       </c>
       <c r="I26" t="n">
-        <v>2.6264</v>
+        <v>2.626399999999999</v>
       </c>
       <c r="J26" t="n">
         <v>9.004899999999999</v>
@@ -2482,13 +2482,13 @@
         <v>10.438</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.0252</v>
+        <v>0.3337999999999998</v>
       </c>
       <c r="T26" t="n">
         <v>-1.0982</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9268999999999998</v>
+        <v>1.4321</v>
       </c>
       <c r="V26" t="n">
         <v>-3.3584</v>
@@ -2497,7 +2497,7 @@
         <v>4.0674</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.4257</v>
+        <v>-7.425700000000001</v>
       </c>
     </row>
   </sheetData>
